--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ.xlsx
@@ -3107,11 +3107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="36380705"/>
-        <c:axId val="57782162"/>
+        <c:axId val="65051792"/>
+        <c:axId val="28215513"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="36380705"/>
+        <c:axId val="65051792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3145,7 +3145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57782162"/>
+        <c:crossAx val="28215513"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3157,7 +3157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="57782162"/>
+        <c:axId val="28215513"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3200,7 +3200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36380705"/>
+        <c:crossAx val="65051792"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5918,11 +5918,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="60639873"/>
-        <c:axId val="7055193"/>
+        <c:axId val="44444360"/>
+        <c:axId val="35109074"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="60639873"/>
+        <c:axId val="44444360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +5954,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7055193"/>
+        <c:crossAx val="35109074"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5965,7 +5965,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="7055193"/>
+        <c:axId val="35109074"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6041,7 +6041,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60639873"/>
+        <c:crossAx val="44444360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9805,7 +9805,7 @@
       </c>
       <c r="AW20" s="29" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2971,$B$3:$B$2971)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="29" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2971,$B$3:$B$2971)</f>
@@ -22424,7 +22424,7 @@
         <v>46142</v>
       </c>
       <c r="B244" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="F244" s="62" t="n">
         <v>46142</v>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ.xlsx
@@ -3107,11 +3107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="65051792"/>
-        <c:axId val="28215513"/>
+        <c:axId val="29905436"/>
+        <c:axId val="73278318"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="65051792"/>
+        <c:axId val="29905436"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3145,7 +3145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28215513"/>
+        <c:crossAx val="73278318"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3157,7 +3157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="28215513"/>
+        <c:axId val="73278318"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3200,7 +3200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65051792"/>
+        <c:crossAx val="29905436"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5918,11 +5918,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="44444360"/>
-        <c:axId val="35109074"/>
+        <c:axId val="74913916"/>
+        <c:axId val="58976821"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="44444360"/>
+        <c:axId val="74913916"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +5954,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35109074"/>
+        <c:crossAx val="58976821"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5965,7 +5965,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="35109074"/>
+        <c:axId val="58976821"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6041,7 +6041,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44444360"/>
+        <c:crossAx val="74913916"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ.xlsx
@@ -3107,11 +3107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="29905436"/>
-        <c:axId val="73278318"/>
+        <c:axId val="71919314"/>
+        <c:axId val="61946910"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="29905436"/>
+        <c:axId val="71919314"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3145,7 +3145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73278318"/>
+        <c:crossAx val="61946910"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3157,7 +3157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="73278318"/>
+        <c:axId val="61946910"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3200,7 +3200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29905436"/>
+        <c:crossAx val="71919314"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5918,11 +5918,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74913916"/>
-        <c:axId val="58976821"/>
+        <c:axId val="17022202"/>
+        <c:axId val="79729191"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="74913916"/>
+        <c:axId val="17022202"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +5954,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58976821"/>
+        <c:crossAx val="79729191"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5965,7 +5965,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="58976821"/>
+        <c:axId val="79729191"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6041,7 +6041,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74913916"/>
+        <c:crossAx val="17022202"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ.xlsx
@@ -3107,11 +3107,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="71919314"/>
-        <c:axId val="61946910"/>
+        <c:axId val="25867181"/>
+        <c:axId val="90472444"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="71919314"/>
+        <c:axId val="25867181"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3145,7 +3145,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61946910"/>
+        <c:crossAx val="90472444"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3157,7 +3157,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="61946910"/>
+        <c:axId val="90472444"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3200,7 +3200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71919314"/>
+        <c:crossAx val="25867181"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5918,11 +5918,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="17022202"/>
-        <c:axId val="79729191"/>
+        <c:axId val="510193"/>
+        <c:axId val="45628596"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="17022202"/>
+        <c:axId val="510193"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +5954,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79729191"/>
+        <c:crossAx val="45628596"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5965,7 +5965,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79729191"/>
+        <c:axId val="45628596"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6041,7 +6041,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17022202"/>
+        <c:crossAx val="510193"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
